--- a/data/trans_bre/IP2004-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Edad-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,04</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,2</t>
+          <t>-1,63; 1,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,48</t>
+          <t>-0,68; 3,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -0,95</t>
+          <t>-5,12; -0,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,93; 362,86</t>
+          <t>-88,53; 401,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,94; —</t>
+          <t>-62,85; 1063,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 3,73</t>
+          <t>-4,91; 3,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,69</t>
+          <t>-4,72; 1,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 5,92</t>
+          <t>-0,34; 5,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,27</t>
+          <t>-2,69; 2,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,98; 105,43</t>
+          <t>-66,54; 125,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-79,08; 113,22</t>
+          <t>-83,14; 117,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 495,92</t>
+          <t>-18,17; 556,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-80,37; 234,04</t>
+          <t>-81,39; 229,89</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 5,02</t>
+          <t>-2,42; 5,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,28</t>
+          <t>-1,81; 6,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,58</t>
+          <t>-3,51; 3,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,2</t>
+          <t>-2,89; 1,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,21; 145,06</t>
+          <t>-34,99; 150,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 201,1</t>
+          <t>-31,22; 224,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,76; 211,56</t>
+          <t>-61,99; 145,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-85,1; 96,46</t>
+          <t>-82,0; 129,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,86</t>
+          <t>-1,32; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,15</t>
+          <t>-1,01; 2,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,59</t>
+          <t>-0,03; 2,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,12</t>
+          <t>-2,31; 0,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 78,06</t>
+          <t>-35,41; 73,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 113,67</t>
+          <t>-32,31; 126,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 229,47</t>
+          <t>-4,7; 229,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-78,1; 14,18</t>
+          <t>-77,8; 12,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Edad-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 4,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,2</t>
+          <t>-1,41; 1,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,16</t>
+          <t>-0,5; 3,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; -0,86</t>
+          <t>-5,76; -1,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,53; 401,19</t>
+          <t>-85,44; 423,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,85; 1063,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 3,77</t>
+          <t>-5,0; 3,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 1,79</t>
+          <t>-4,82; 1,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,74</t>
+          <t>-0,26; 5,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,18</t>
+          <t>-3,12; 1,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-66,54; 125,02</t>
+          <t>-68,26; 105,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,14; 117,94</t>
+          <t>-82,83; 101,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 556,61</t>
+          <t>-24,07; 578,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,39; 229,89</t>
+          <t>-84,39; 196,79</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 5,06</t>
+          <t>-2,45; 5,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 6,62</t>
+          <t>-2,4; 5,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 3,73</t>
+          <t>-3,65; 3,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,25</t>
+          <t>-3,1; 1,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 150,57</t>
+          <t>-36,19; 141,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 224,2</t>
+          <t>-43,6; 189,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,99; 145,85</t>
+          <t>-60,08; 174,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,0; 129,31</t>
+          <t>-83,94; 113,64</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,82</t>
+          <t>-1,21; 1,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,26</t>
+          <t>-0,82; 2,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,56</t>
+          <t>-0,11; 2,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,07</t>
+          <t>-2,39; 0,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 73,28</t>
+          <t>-33,81; 71,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 126,16</t>
+          <t>-24,56; 129,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 229,02</t>
+          <t>-8,03; 252,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-77,8; 12,29</t>
+          <t>-77,15; 24,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Edad-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,2</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,52</t>
+          <t>-2,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,25</t>
+          <t>-1,41; 1,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,52</t>
+          <t>-0,42; 3,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,76; -1,08</t>
+          <t>-5,84; -1,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,44; 423,24</t>
+          <t>-88,93; 362,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-50,94; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-18,5%</t>
+          <t>-17,79%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,61</t>
+          <t>-5,08; 3,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,65</t>
+          <t>-4,43; 1,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,61</t>
+          <t>-0,5; 5,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,9</t>
+          <t>-2,96; 2,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-68,26; 105,57</t>
+          <t>-65,98; 105,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-82,83; 101,54</t>
+          <t>-79,08; 113,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 578,75</t>
+          <t>-27,12; 495,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-84,39; 196,79</t>
+          <t>-82,6; 244,87</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-35,68%</t>
+          <t>-22,76%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 5,0</t>
+          <t>-2,78; 5,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 5,88</t>
+          <t>-1,82; 6,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,91</t>
+          <t>-3,07; 4,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,28</t>
+          <t>-2,76; 1,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 141,25</t>
+          <t>-37,21; 145,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 189,77</t>
+          <t>-30,1; 201,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,08; 174,43</t>
+          <t>-53,76; 211,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,94; 113,64</t>
+          <t>-80,95; 162,18</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-48,9%</t>
+          <t>-43,49%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,8</t>
+          <t>-1,33; 1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,32</t>
+          <t>-0,77; 2,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,65</t>
+          <t>-0,18; 2,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,18</t>
+          <t>-2,28; 0,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 71,87</t>
+          <t>-34,82; 78,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 129,53</t>
+          <t>-27,86; 113,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 252,36</t>
+          <t>-13,18; 229,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-77,15; 24,01</t>
+          <t>-76,07; 24,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,159 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8443367006423853</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,04</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.04149252148274</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,65</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-8,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>127,96%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,41; 1,2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,42; 3,48</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,99</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,84; -1,0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-88,93; 362,86</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-50,94; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.08394202034617149</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.237325012079056</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9218285345425974</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.651539228728551</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.08035137558796604</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.279568621811959</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,27</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,51</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-14,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-33,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>114,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-17,79%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.410977121659031</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.4232222901575445</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.842220393344378</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.8893235760202015</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5093800767758442</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,08; 3,73</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,43; 1,69</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,5; 5,92</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,96; 2,35</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-65,98; 105,43</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-79,08; 113,22</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-27,12; 495,92</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-82,6; 244,87</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.198800317225556</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.482275097127475</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.993307368302966</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-1.003342238771725</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3.628555295782737</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +779,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-22,76%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.7772550984691484</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.265576496628637</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.50835368681093</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.4142094912101588</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1414626709013183</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3318661744063691</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1.140526152212035</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1779205154265872</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,78; 5,02</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,82; 6,28</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,07; 4,58</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,76; 1,73</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-37,21; 145,06</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-30,1; 201,1</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-53,76; 211,56</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-80,95; 162,18</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.079181104466878</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.43072341096468</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.5017469134712724</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.955403723810199</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6598490632367977</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.7908140601522455</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.2712199260249558</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.8259623673259017</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.734569293267517</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.691284591158252</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.920360092488044</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.352381943697885</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.054260202380116</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.132207500640897</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>4.959160544931202</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.448654325856506</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.210206510088289</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.161647053013055</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.3178538300642485</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.5298789215399076</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.2191625588384223</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.4571643777627843</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.07576816366250673</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2276380483390065</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.775258653225012</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.821339740042458</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.074106356791819</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.762697432314993</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3720981050137002</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3009861333782317</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5375967258561736</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.8095038225439584</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.018240072313878</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.278951685509329</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.579330879544307</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.729335575396449</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.450608769823629</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.011020558111148</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.115604023021392</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.621805964765801</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>72,81%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-43,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 1,86</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,77; 2,15</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,18; 2,59</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,28; 0,29</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-34,82; 78,06</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-27,86; 113,67</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-13,18; 229,47</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-76,07; 24,91</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.2628764582646014</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.7262272942149459</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.189309266810171</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.9860163449720621</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.08304144455482446</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2978593811239766</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.7281006934068505</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.4348543829021261</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.332439225733758</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.7687160474182222</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.1768790824133249</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.281339853793956</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3482201138500999</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2786012847452998</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1317998919663743</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.7606903478589344</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.857948693066783</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.149107267995875</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.593970723103002</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.292869703831217</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.7805517430739226</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.136653626205526</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2.294659853369024</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.2491153656959051</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1077,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
